--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS PRIVATE LAND ONLY ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS PRIVATE LAND ONLY ANY LEGAL WEAPON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -645,7 +650,8 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -710,7 +716,8 @@
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
@@ -775,7 +782,8 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -844,7 +852,8 @@
           <t>5.4</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -913,7 +922,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -982,7 +992,8 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -1051,7 +1062,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1120,7 +1132,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
@@ -1189,7 +1202,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
@@ -1258,7 +1272,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -1327,7 +1342,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -1396,7 +1412,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -1465,7 +1482,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
@@ -1534,7 +1552,8 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
@@ -1603,7 +1622,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1672,7 +1692,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -1741,7 +1762,8 @@
           <t>6.4</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
@@ -1806,7 +1828,8 @@
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -1875,7 +1898,8 @@
           <t>8.6</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -1940,7 +1964,8 @@
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -2005,7 +2030,8 @@
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -2074,7 +2100,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -2143,7 +2170,8 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -2212,7 +2240,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -2276,8 +2305,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
@@ -2342,7 +2376,8 @@
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -2399,7 +2434,8 @@
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
